--- a/AAII_Financials/Yearly/SLMT_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SLMT_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="221" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="92">
   <si>
     <t>SLMT</t>
   </si>
@@ -715,10 +715,10 @@
         <v>5300</v>
       </c>
       <c r="E8" s="3">
-        <v>3000</v>
+        <v>1200</v>
       </c>
       <c r="F8" s="3">
-        <v>1300</v>
+        <v>300</v>
       </c>
       <c r="G8" s="3">
         <v>200</v>
@@ -744,11 +744,11 @@
       <c r="D9" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="3">
-        <v>300</v>
-      </c>
-      <c r="F9" s="3">
-        <v>100</v>
+      <c r="E9" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G9" s="3">
         <v>100</v>
@@ -775,10 +775,10 @@
         <v>5300</v>
       </c>
       <c r="E10" s="3">
-        <v>2700</v>
+        <v>1200</v>
       </c>
       <c r="F10" s="3">
-        <v>1200</v>
+        <v>300</v>
       </c>
       <c r="G10" s="3">
         <v>100</v>
@@ -878,11 +878,11 @@
       <c r="D14" s="3">
         <v>96300</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
+      <c r="E14" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>3</v>
@@ -912,7 +912,7 @@
         <v>100</v>
       </c>
       <c r="F15" s="3">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="G15" s="3">
         <v>0</v>
@@ -950,10 +950,10 @@
         <v>360500</v>
       </c>
       <c r="E17" s="3">
-        <v>8700</v>
+        <v>5600</v>
       </c>
       <c r="F17" s="3">
-        <v>7200</v>
+        <v>4500</v>
       </c>
       <c r="G17" s="3">
         <v>1500</v>
@@ -980,10 +980,10 @@
         <v>-355200</v>
       </c>
       <c r="E18" s="3">
-        <v>-5800</v>
+        <v>-4400</v>
       </c>
       <c r="F18" s="3">
-        <v>-5900</v>
+        <v>-4100</v>
       </c>
       <c r="G18" s="3">
         <v>-1300</v>
@@ -1024,7 +1024,7 @@
         <v>-7400</v>
       </c>
       <c r="E20" s="3">
-        <v>-600</v>
+        <v>-400</v>
       </c>
       <c r="F20" s="3">
         <v>-600</v>
@@ -1054,10 +1054,10 @@
         <v>-346400</v>
       </c>
       <c r="E21" s="3">
-        <v>-5100</v>
+        <v>-3900</v>
       </c>
       <c r="F21" s="3">
-        <v>-5100</v>
+        <v>-3500</v>
       </c>
       <c r="G21" s="3">
         <v>-1300</v>
@@ -1084,10 +1084,10 @@
         <v>300</v>
       </c>
       <c r="E22" s="3">
-        <v>100</v>
-      </c>
-      <c r="F22" s="3">
-        <v>0</v>
+        <v>0</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G22" s="3">
         <v>0</v>
@@ -1114,10 +1114,10 @@
         <v>-444300</v>
       </c>
       <c r="E23" s="3">
-        <v>-5300</v>
+        <v>-4000</v>
       </c>
       <c r="F23" s="3">
-        <v>-5400</v>
+        <v>-3500</v>
       </c>
       <c r="G23" s="3">
         <v>-1300</v>
@@ -1143,11 +1143,11 @@
       <c r="D24" s="3">
         <v>-1300</v>
       </c>
-      <c r="E24" s="3">
-        <v>0</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0</v>
+      <c r="E24" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F24" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G24" s="3" t="s">
         <v>3</v>
@@ -1204,10 +1204,10 @@
         <v>-443000</v>
       </c>
       <c r="E26" s="3">
-        <v>-5200</v>
+        <v>-4000</v>
       </c>
       <c r="F26" s="3">
-        <v>-5400</v>
+        <v>-3500</v>
       </c>
       <c r="G26" s="3">
         <v>-1300</v>
@@ -1294,10 +1294,10 @@
         <v>-800</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-1300</v>
       </c>
       <c r="F29" s="3">
-        <v>0</v>
+        <v>-1900</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -1384,7 +1384,7 @@
         <v>7400</v>
       </c>
       <c r="E32" s="3">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="F32" s="3">
         <v>600</v>
@@ -1624,10 +1624,10 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>13800</v>
+        <v>13900</v>
       </c>
       <c r="E43" s="3">
-        <v>1400</v>
+        <v>400</v>
       </c>
       <c r="F43" s="3">
         <v>600</v>
@@ -1656,8 +1656,8 @@
       <c r="D44" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E44" s="3">
-        <v>0</v>
+      <c r="E44" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>3</v>
@@ -1686,8 +1686,8 @@
       <c r="D45" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E45" s="3" t="s">
-        <v>3</v>
+      <c r="E45" s="3">
+        <v>800</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>3</v>
@@ -1717,7 +1717,7 @@
         <v>67700</v>
       </c>
       <c r="E46" s="3">
-        <v>3000</v>
+        <v>3100</v>
       </c>
       <c r="F46" s="3">
         <v>3300</v>
@@ -1746,8 +1746,8 @@
       <c r="D47" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E47" s="3">
-        <v>2600</v>
+      <c r="E47" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F47" s="3">
         <v>500</v>
@@ -1776,8 +1776,8 @@
       <c r="D48" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E48" s="3">
-        <v>1900</v>
+      <c r="E48" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="F48" s="3">
         <v>1200</v>
@@ -1807,7 +1807,7 @@
         <v>13900</v>
       </c>
       <c r="E49" s="3">
-        <v>2900</v>
+        <v>900</v>
       </c>
       <c r="F49" s="3">
         <v>4500</v>
@@ -1896,8 +1896,8 @@
       <c r="D52" s="3">
         <v>111400</v>
       </c>
-      <c r="E52" s="3" t="s">
-        <v>3</v>
+      <c r="E52" s="3">
+        <v>6500</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>3</v>
@@ -2015,7 +2015,7 @@
         <v>16200</v>
       </c>
       <c r="E57" s="3">
-        <v>3300</v>
+        <v>1500</v>
       </c>
       <c r="F57" s="3">
         <v>3900</v>
@@ -2045,7 +2045,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="3">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="F58" s="3">
         <v>300</v>
@@ -2075,7 +2075,7 @@
         <v>1500</v>
       </c>
       <c r="E59" s="3">
-        <v>300</v>
+        <v>2800</v>
       </c>
       <c r="F59" s="3">
         <v>600</v>
@@ -2135,7 +2135,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="3">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="F61" s="3">
         <v>900</v>
@@ -2165,7 +2165,7 @@
         <v>4100</v>
       </c>
       <c r="E62" s="3">
-        <v>1400</v>
+        <v>2100</v>
       </c>
       <c r="F62" s="3">
         <v>200</v>
@@ -2705,13 +2705,13 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>1400</v>
+        <v>0</v>
       </c>
       <c r="E83" s="3">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="F83" s="3">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="G83" s="3">
         <v>100</v>
@@ -2888,10 +2888,10 @@
         <v>-12600</v>
       </c>
       <c r="E89" s="3">
+        <v>-3100</v>
+      </c>
+      <c r="F89" s="3">
         <v>-3200</v>
-      </c>
-      <c r="F89" s="3">
-        <v>-2700</v>
       </c>
       <c r="G89" s="3">
         <v>-1000</v>
@@ -2932,10 +2932,10 @@
         <v>0</v>
       </c>
       <c r="E91" s="3">
-        <v>-200</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-200</v>
+        <v>0</v>
+      </c>
+      <c r="F91" s="3" t="s">
+        <v>3</v>
       </c>
       <c r="G91" s="3">
         <v>0</v>
@@ -3189,7 +3189,7 @@
         <v>2800</v>
       </c>
       <c r="F100" s="3">
-        <v>7000</v>
+        <v>7400</v>
       </c>
       <c r="G100" s="3">
         <v>1300</v>
@@ -3246,10 +3246,10 @@
         <v>17200</v>
       </c>
       <c r="E102" s="3">
-        <v>-800</v>
+        <v>-700</v>
       </c>
       <c r="F102" s="3">
-        <v>2200</v>
+        <v>2100</v>
       </c>
       <c r="G102" s="3">
         <v>300</v>
